--- a/reports/pdf_weekly_20260828.xlsx
+++ b/reports/pdf_weekly_20260828.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-08-24 ~ 2026-08-28  (5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>주간 변화  ·  2026-08-24 ~ 2026-08-28  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,575억   ·   현금 67억(1.4%)      주말 2026-08-28  vs  주초 2026-08-24      매수 9종목  /  매도 12종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억   ·   현금 62억(1.3%)      주말 2026-08-28  vs  주초 2026-08-24      매수 12종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -663,23 +663,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (신규)</t>
+          <t>와이씨  (신규)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3633269250</v>
+        <v>1885602810</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>0.00%→0.41%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0→89</t>
+          <t>0→147</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -688,42 +688,42 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-106</v>
+        <v>-139</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-7228436800</v>
+        <v>-9521625100</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>5.77%→3.99%</t>
+          <t>5.77%→3.45%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>372→266</t>
+          <t>372→233</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>아이티센글로벌  (신규)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>877160700</v>
+        <v>3450463250</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.72%→0.90%</t>
+          <t>0.00%→0.75%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>287→365</t>
+          <t>0→89</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -735,7 +735,7 @@
         <v>-67</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-884195650</v>
+        <v>-917223970</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>와이씨  (신규)</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>941245500</v>
+        <v>845919360</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.21%</t>
+          <t>0.72%→0.85%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→75</t>
+          <t>287→365</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>888663100</v>
+        <v>2126403500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.61%</t>
+          <t>2.08%→2.65%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>420→454</t>
+          <t>196→237</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -820,130 +820,130 @@
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-22</v>
+        <v>-27</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1685512400</v>
+        <v>-2107404000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.67%→1.21%</t>
+          <t>1.67%→1.13%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>94→72</t>
+          <t>94→67</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>869304150</v>
+        <v>888663100</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.62%→1.79%</t>
+          <t>2.75%→2.56%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>276→309</t>
+          <t>420→454</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코세스  (편출)</t>
+          <t>가온칩스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-430261650</v>
+        <v>-945867000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.86%→1.58%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>175→155</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4408911000</v>
+        <v>755769300</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>1.62%→1.53%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>276→309</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코세스  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-8</v>
+        <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-925943200</v>
+        <v>-430261650</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>4.24%→4.38%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>180→172</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4524448500</v>
+        <v>2347722000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.00%</t>
+          <t>3.63%→4.53%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0→11</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -952,1033 +952,1937 @@
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-404740700</v>
+        <v>-809481400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.50%→0.42%</t>
+          <t>0.50%→0.32%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>40→33</t>
+          <t>40→26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>815848800</v>
+        <v>4482855000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.81%→0.97%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>35→43</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-205964850</v>
+        <v>-2880735000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.55%→0.49%</t>
+          <t>3.00%→2.21%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>50→39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
+          <t>이오테크닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>6679608000</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.44%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>0→16</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>한국피아이엠</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-394778800</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.22%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>29→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>439504650</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1.14%→1.34%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>118→127</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>-1042610400</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>4.24%→4.84%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>180→172</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>861036800</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>0.81%→1.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>35→43</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-209559350</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>0.55%→0.49%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>83→76</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C17" s="11" t="n">
         <v>959731500</v>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>7.11%→6.83%</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>7.11%→6.70%</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>94→97</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-348769200</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>0.55%→0.41%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>39→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>솔브레인홀딩스</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H18" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-217467250</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>0.51%→0.50%</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="I18" s="15" t="n">
+        <v>-225940000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.51%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>57→52</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>에스엔시스</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-94278600</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>0.63%→0.60%</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="I19" s="15" t="n">
+        <v>-97975800</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>0.63%→0.61%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>120→116</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>펌텍코리아</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>-182087100</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>0.55%→0.48%</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>39→36</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>로보티즈</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>-771790500</v>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>3.00%→2.66%</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>50→47</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,904억   ·   현금 25억(0.6%)      주말 2026-08-28  vs  주초 2026-08-24      매수 5종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-    </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-409156800</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>1.54%→1.35%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>65→61</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억   ·   현금 25억(0.6%)      주말 2026-08-28  vs  주초 2026-08-24      매수 5종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>한올바이오파마</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>1938499200</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>5.50%→6.39%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>683→741</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-113</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>-1144952160</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>3.02%→2.50%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>1,068→955</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>393687360</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>1.27%→1.43%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>564→607</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-88</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>-978067200</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>0.57%→0.29%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>190→102</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>1129603200</v>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>4.75%→5.08%</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>625→663</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>-1141852800</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>4.71%→4.12%</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>330→308</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>큐라클</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>192186720</v>
+        <v>1976582000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.69%→1.69%</t>
+          <t>5.50%→6.49%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>1,092→1,125</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
+          <t>683→741</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-113</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-1154080300</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>3.02%→2.51%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>1,068→955</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>395406500</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.27%→1.43%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>564→607</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-88</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-1016752000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>0.57%→0.30%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>190→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1133882000</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>4.75%→5.09%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>625→663</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-1161336000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>4.71%→4.18%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>330→308</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>큐라클</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>185568900</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>1.69%→1.63%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>1,092→1,125</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>1867008000</v>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>5.31%→6.08%</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C29" s="11" t="n">
+        <v>1833800000</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>5.31%→5.95%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>93→101</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="19" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 4억(1.5%)      주말 2026-08-28  vs  주초 2026-08-24      매수 8종목  /  매도 9종목</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억   ·   현금 66억(2.5%)      주말 2026-08-28  vs  주초 2026-08-24      매수 6종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>아이티센글로벌  (신규)</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>2894292500</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.11%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>0→110</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-158</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-1636472360</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>1.06%→0.59%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>308→150</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>98923200</v>
+        <v>5395407300</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>3.10%→3.47%</t>
+          <t>4.23%→7.10%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>697→777</t>
+          <t>149→210</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>더블유씨피  (편출)</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-64</v>
+        <v>-144</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-120531200</v>
+        <v>-863164800</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.25%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>395→331</t>
+          <t>144→0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>티엘비  (신규)</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>136163700</v>
+        <v>1533957600</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.49%</t>
+          <t>1.09%→1.67%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>0→47</t>
+          <t>39→60</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>PS일렉트로닉스  (편출)</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-49</v>
+        <v>-116</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-44599800</v>
+        <v>-725242440</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.82%</t>
+          <t>0.30%→0.00%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>907→858</t>
+          <t>116→0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>44252000</v>
+        <v>3526820000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>2.25%→2.42%</t>
+          <t>0.95%→2.36%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>367→393</t>
+          <t>15→35</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>메쥬  (편출)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-48</v>
+        <v>-77</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-37118400</v>
+        <v>-646711450</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>1.44%→1.31%</t>
+          <t>0.26%→0.00%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>516→468</t>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>액트로</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>14652000</v>
+        <v>175058520</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.42%</t>
+          <t>1.72%→1.87%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>154→176</t>
+          <t>350→363</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-35</v>
+        <v>-50</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-91038500</v>
+        <v>-839885000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.14%→2.82%</t>
+          <t>0.62%→0.45%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>335→300</t>
+          <t>120→70</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
+          <t>이오테크닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>3399966000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.30%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>0→12</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-2202868500</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>1.57%→0.69%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>89→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-1472482200</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>4.69%→4.01%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>341→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-7599042500</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>7.57%→3.98%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>83→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억   ·   현금 60억(2.7%)      주말 2026-08-28  vs  주초 2026-08-24      매수 7종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>496</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>2925904000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.32%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>0→496</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-206</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-13398652000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>15.89%→9.23%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>520→314</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>209</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>2245496000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>1.63%→2.67%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>341→550</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>삼성에피스홀딩스  (편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-39</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-4773600000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>39→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>6787080000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>1.05%→4.19%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>66→246</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-2118200000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>12.00%→10.34%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>236→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>2066792000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>3.34%→4.41%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>339→430</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>2214420000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>3.77%→5.00%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>156→195</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>4112640000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>5.61%→8.44%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>85→109</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n"/>
+      <c r="H51" s="17" t="n"/>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>32759000</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.80%→0.76%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>253→258</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="n"/>
+      <c r="H52" s="17" t="n"/>
+      <c r="I52" s="17" t="n"/>
+      <c r="J52" s="17" t="n"/>
+      <c r="K52" s="17" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 5억(1.6%)      주말 2026-08-28  vs  주초 2026-08-24      매수 10종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>95270400</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>2.95%→3.31%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>697→777</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-200246400</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>3.51%→2.81%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>335→267</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>티엘비  (신규)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>140436000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.50%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>0→47</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-60685920</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>2.92%→2.72%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>907→840</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>22982400</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>0.41%→0.50%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>191→229</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-117273600</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>2.57%→2.17%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>395→331</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>68997600</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>0.73%→0.98%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>53→71</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="B60" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>116780400</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.67%→1.09%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>53→86</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-35942400</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>1.37%→1.25%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>516→468</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>43336800</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>2.17%→2.34%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>367→393</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-59544000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>7.66%→7.49%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>724→704</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>15950880</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>0.40%→0.46%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>154→176</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-92066400</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>2.74%→2.43%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>159→140</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>41011200</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>0.95%→1.10%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>104→120</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-91440000</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>3.48%→3.17%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>107→97</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>54532800</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>0.97%→1.17%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>35→42</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-81144000</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>2.74%→2.47%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>95→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>32508000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>0.97%→1.10%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>59→66</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-24321600</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>0.27%→0.19%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>19→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>37699200</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>0.80%→0.94%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>42→49</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="H39" s="15" t="n">
-        <v>-19</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-47311900</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>3.12%→2.96%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>348→329</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>40907200</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>0.96%→1.11%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>104→120</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-19</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-93780200</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>2.82%→2.50%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>159→140</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>씨엠티엑스</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>37917600</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>0.82%→0.96%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>42→49</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-88208000</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>3.40%→3.09%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>107→97</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>54131000</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>0.97%→1.17%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>35→42</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-80882000</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>2.76%→2.49%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>95→85</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-24997200</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.28%→0.20%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>19→13</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억   ·   현금 6억(1.0%)      주말 2026-08-28  vs  주초 2026-08-24      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="H66" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-7171200</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>2.96%→2.95%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>348→345</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 3억(0.5%)      주말 2026-08-28  vs  주초 2026-08-24      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
-      <c r="J48" s="19" t="n"/>
-      <c r="K48" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="20" t="n"/>
+      <c r="J71" s="20" t="n"/>
+      <c r="K71" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="G55:K55"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20260828.xlsx
+++ b/reports/pdf_weekly_20260828.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억   ·   현금 62억(1.3%)      주말 2026-08-28  vs  주초 2026-08-24      매수 12종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억   ·   현금 31억(0.7%)      주말 2026-08-28  vs  주초 2026-08-24      매수 12종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2347722000</v>
+        <v>4482855000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.53%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4482855000</v>
+        <v>2347722000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.53%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>한국피아이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-394778800</v>
+        <v>-1042610400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.22%</t>
+          <t>4.24%→4.84%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>29→21</t>
+          <t>180→172</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>한국피아이엠</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1042610400</v>
+        <v>-394778800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>4.24%→4.84%</t>
+          <t>0.36%→0.22%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>180→172</t>
+          <t>29→21</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억   ·   현금 25억(0.6%)      주말 2026-08-28  vs  주초 2026-08-24      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억   ·   현금 12억(0.3%)      주말 2026-08-28  vs  주초 2026-08-24      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1552,7 +1552,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억   ·   현금 66억(2.5%)      주말 2026-08-28  vs  주초 2026-08-24      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억   ·   현금 33억(1.2%)      주말 2026-08-28  vs  주초 2026-08-24      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억   ·   현금 60억(2.7%)      주말 2026-08-28  vs  주초 2026-08-24      매수 7종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억   ·   현금 30억(1.3%)      주말 2026-08-28  vs  주초 2026-08-24      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2294,7 +2294,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 5억(1.6%)      주말 2026-08-28  vs  주초 2026-08-24      매수 10종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 2억(0.8%)      주말 2026-08-28  vs  주초 2026-08-24      매수 10종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>

--- a/reports/pdf_weekly_20260828.xlsx
+++ b/reports/pdf_weekly_20260828.xlsx
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4482855000</v>
+        <v>2347722000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.53%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2347722000</v>
+        <v>4482855000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.53%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>한국피아이엠</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1042610400</v>
+        <v>-394778800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>4.24%→4.84%</t>
+          <t>0.36%→0.22%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>180→172</t>
+          <t>29→21</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>한국피아이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-394778800</v>
+        <v>-1042610400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.22%</t>
+          <t>4.24%→4.84%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>29→21</t>
+          <t>180→172</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260828.xlsx
+++ b/reports/pdf_weekly_20260828.xlsx
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2347722000</v>
+        <v>4482855000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.53%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4482855000</v>
+        <v>2347722000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.53%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1224,23 +1224,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-97975800</v>
+        <v>-409156800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.61%</t>
+          <t>1.54%→1.35%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1252,23 +1252,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-409156800</v>
+        <v>-97975800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.35%</t>
+          <t>0.63%→0.61%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -2668,67 +2668,67 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-91440000</v>
+        <v>-81144000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>3.48%→3.17%</t>
+          <t>2.74%→2.47%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>54532800</v>
+        <v>37699200</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.17%</t>
+          <t>0.80%→0.94%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-81144000</v>
+        <v>-91440000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.74%→2.47%</t>
+          <t>3.48%→3.17%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2779,23 +2779,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>37699200</v>
+        <v>54532800</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.80%→0.94%</t>
+          <t>0.97%→1.17%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
